--- a/Pomiary.xlsx
+++ b/Pomiary.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a3eea4af91086274/Pulpit/SBD/P1/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a3eea4af91086274/Pulpit/SEM5/SBD/P1/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2FCF4A24-72F7-4805-86B8-F02B7F7B739A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="27" documentId="8_{2FCF4A24-72F7-4805-86B8-F02B7F7B739A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B432F5D7-AA74-47C7-A04E-2FA9670C920D}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{63E0899F-1F7B-41C1-81BE-D2DEB1B2E785}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{63E0899F-1F7B-41C1-81BE-D2DEB1B2E785}"/>
   </bookViews>
   <sheets>
     <sheet name="Arkusz1" sheetId="1" r:id="rId1"/>
@@ -76,7 +76,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="#,##0.00\ _z_ł"/>
+    <numFmt numFmtId="164" formatCode="#,##0.00\ _z_ł"/>
   </numFmts>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
@@ -113,7 +113,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -253,46 +253,46 @@
                   <c:v>19</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>25</c:v>
+                  <c:v>23</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>27</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>63</c:v>
+                  <c:v>58</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>100</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>231</c:v>
+                  <c:v>214</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>446</c:v>
+                  <c:v>444</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>985</c:v>
+                  <c:v>926</c:v>
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>2014</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>4439</c:v>
+                  <c:v>4186</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>9078</c:v>
+                  <c:v>9074</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>19929</c:v>
+                  <c:v>18914</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>40630</c:v>
+                  <c:v>40634</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>88565</c:v>
+                  <c:v>84466</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0</c:v>
+                  <c:v>179618</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1590,15 +1590,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E0FACBD2-E050-4C25-B7F3-B372F54F54CB}">
   <dimension ref="A1:K16"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="5" width="8.88671875" style="1"/>
-    <col min="6" max="6" width="12.88671875" style="2" customWidth="1"/>
-    <col min="7" max="7" width="13.44140625" style="2" customWidth="1"/>
+    <col min="2" max="5" width="8.85546875" style="1"/>
+    <col min="6" max="6" width="12.85546875" style="2" customWidth="1"/>
+    <col min="7" max="7" width="13.42578125" style="2" customWidth="1"/>
     <col min="8" max="8" width="13" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>7</v>
       </c>
@@ -1633,7 +1633,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>256</v>
       </c>
@@ -1655,11 +1655,11 @@
         <v>3.1</v>
       </c>
       <c r="G2" s="2">
-        <f>(2*B2/$A$2)*(1.04*LOG(B2/2,2)+1.5+IF(MOD(ROUND(K2,0)-1,3)=0,0,1))</f>
+        <f t="shared" ref="G2:G16" si="0">(2*B2/$A$2)*(1.04*LOG(B2/2,2)+1.5+IF(MOD(ROUND(K2,0)-1,3)=0,0,1))</f>
         <v>3.35</v>
       </c>
       <c r="H2" s="1">
-        <f>(E2-F2)/E2</f>
+        <f t="shared" ref="H2:H16" si="1">(E2-F2)/E2</f>
         <v>0.83684210526315794</v>
       </c>
       <c r="I2" s="1">
@@ -1674,45 +1674,45 @@
         <v>7.1999999999999993</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B3" s="1">
         <v>128</v>
       </c>
       <c r="C3" s="1">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D3" s="1">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E3" s="1">
         <f>SUM(C3:D3)</f>
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F3" s="2">
-        <f t="shared" ref="F3:F16" si="0">(2*B3/$A$2)*(1.04*LOG(B3/2,2)+1)</f>
+        <f t="shared" ref="F3:F16" si="2">(2*B3/$A$2)*(1.04*LOG(B3/2,2)+1)</f>
         <v>7.24</v>
       </c>
       <c r="G3" s="2">
-        <f>(2*B3/$A$2)*(1.04*LOG(B3/2,2)+1.5+IF(MOD(ROUND(K3,0)-1,3)=0,0,1))</f>
+        <f t="shared" si="0"/>
         <v>8.74</v>
       </c>
       <c r="H3" s="1">
-        <f>(E3-F3)/E3</f>
-        <v>0.71039999999999992</v>
+        <f t="shared" si="1"/>
+        <v>0.68521739130434778</v>
       </c>
       <c r="I3" s="1">
-        <f t="shared" ref="I3:I16" si="1">(E3-G3)/E3</f>
-        <v>0.65039999999999987</v>
+        <f t="shared" ref="I3:I16" si="3">(E3-G3)/E3</f>
+        <v>0.62</v>
       </c>
       <c r="J3" s="1">
         <v>9</v>
       </c>
       <c r="K3" s="1">
-        <f t="shared" ref="K3:K16" si="2">1.44*LOG(B3/2,2)</f>
+        <f t="shared" ref="K3:K16" si="4">1.44*LOG(B3/2,2)</f>
         <v>8.64</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B4" s="1">
         <v>256</v>
       </c>
@@ -1723,72 +1723,72 @@
         <v>12</v>
       </c>
       <c r="E4" s="1">
-        <f t="shared" ref="E4:E16" si="3">SUM(C4:D4)</f>
+        <f t="shared" ref="E4:E16" si="5">SUM(C4:D4)</f>
         <v>27</v>
       </c>
       <c r="F4" s="2">
+        <f t="shared" si="2"/>
+        <v>16.560000000000002</v>
+      </c>
+      <c r="G4" s="2">
         <f t="shared" si="0"/>
-        <v>16.560000000000002</v>
-      </c>
-      <c r="G4" s="2">
-        <f>(2*B4/$A$2)*(1.04*LOG(B4/2,2)+1.5+IF(MOD(ROUND(K4,0)-1,3)=0,0,1))</f>
         <v>17.560000000000002</v>
       </c>
       <c r="H4" s="1">
-        <f>(E4-F4)/E4</f>
+        <f t="shared" si="1"/>
         <v>0.3866666666666666</v>
       </c>
       <c r="I4" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0.34962962962962957</v>
       </c>
       <c r="J4" s="1">
         <v>10</v>
       </c>
       <c r="K4" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>10.08</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B5" s="1">
         <v>512</v>
       </c>
       <c r="C5" s="1">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="D5" s="1">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="E5" s="1">
+        <f t="shared" si="5"/>
+        <v>58</v>
+      </c>
+      <c r="F5" s="2">
+        <f t="shared" si="2"/>
+        <v>37.28</v>
+      </c>
+      <c r="G5" s="2">
+        <f t="shared" si="0"/>
+        <v>43.28</v>
+      </c>
+      <c r="H5" s="1">
+        <f t="shared" si="1"/>
+        <v>0.35724137931034483</v>
+      </c>
+      <c r="I5" s="1">
         <f t="shared" si="3"/>
-        <v>63</v>
-      </c>
-      <c r="F5" s="2">
-        <f t="shared" si="0"/>
-        <v>37.28</v>
-      </c>
-      <c r="G5" s="2">
-        <f>(2*B5/$A$2)*(1.04*LOG(B5/2,2)+1.5+IF(MOD(ROUND(K5,0)-1,3)=0,0,1))</f>
-        <v>43.28</v>
-      </c>
-      <c r="H5" s="1">
-        <f>(E5-F5)/E5</f>
-        <v>0.40825396825396826</v>
-      </c>
-      <c r="I5" s="1">
-        <f t="shared" si="1"/>
-        <v>0.31301587301587303</v>
+        <v>0.25379310344827583</v>
       </c>
       <c r="J5" s="1">
         <v>12</v>
       </c>
       <c r="K5" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>11.52</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B6" s="1">
         <v>1024</v>
       </c>
@@ -1799,11 +1799,11 @@
         <v>47</v>
       </c>
       <c r="E6" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>100</v>
       </c>
       <c r="F6" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>82.88</v>
       </c>
       <c r="G6" s="2">
@@ -1811,136 +1811,136 @@
         <v>86.88</v>
       </c>
       <c r="H6" s="1">
-        <f>(E6-F6)/E6</f>
+        <f t="shared" si="1"/>
         <v>0.17120000000000005</v>
       </c>
       <c r="I6" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0.13120000000000004</v>
       </c>
       <c r="J6" s="1">
         <v>13</v>
       </c>
       <c r="K6" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>12.959999999999999</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B7" s="1">
         <v>2048</v>
       </c>
       <c r="C7" s="1">
-        <v>121</v>
+        <v>112</v>
       </c>
       <c r="D7" s="1">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="E7" s="1">
+        <f t="shared" si="5"/>
+        <v>214</v>
+      </c>
+      <c r="F7" s="2">
+        <f t="shared" si="2"/>
+        <v>182.4</v>
+      </c>
+      <c r="G7" s="2">
+        <f t="shared" si="0"/>
+        <v>206.4</v>
+      </c>
+      <c r="H7" s="1">
+        <f t="shared" si="1"/>
+        <v>0.14766355140186913</v>
+      </c>
+      <c r="I7" s="1">
         <f t="shared" si="3"/>
-        <v>231</v>
-      </c>
-      <c r="F7" s="2">
-        <f t="shared" si="0"/>
-        <v>182.4</v>
-      </c>
-      <c r="G7" s="2">
-        <f>(2*B7/$A$2)*(1.04*LOG(B7/2,2)+1.5+IF(MOD(ROUND(K7,0)-1,3)=0,0,1))</f>
-        <v>206.4</v>
-      </c>
-      <c r="H7" s="1">
-        <f>(E7-F7)/E7</f>
-        <v>0.21038961038961038</v>
-      </c>
-      <c r="I7" s="1">
-        <f t="shared" si="1"/>
-        <v>0.10649350649350647</v>
+        <v>3.551401869158876E-2</v>
       </c>
       <c r="J7" s="1">
         <v>15</v>
       </c>
       <c r="K7" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>14.399999999999999</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B8" s="1">
         <v>4096</v>
       </c>
       <c r="C8" s="1">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D8" s="1">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="E8" s="1">
+        <f t="shared" si="5"/>
+        <v>444</v>
+      </c>
+      <c r="F8" s="2">
+        <f t="shared" si="2"/>
+        <v>398.08000000000004</v>
+      </c>
+      <c r="G8" s="2">
+        <f t="shared" si="0"/>
+        <v>414.08000000000004</v>
+      </c>
+      <c r="H8" s="1">
+        <f t="shared" si="1"/>
+        <v>0.10342342342342332</v>
+      </c>
+      <c r="I8" s="1">
         <f t="shared" si="3"/>
-        <v>446</v>
-      </c>
-      <c r="F8" s="2">
-        <f t="shared" si="0"/>
-        <v>398.08000000000004</v>
-      </c>
-      <c r="G8" s="2">
-        <f>(2*B8/$A$2)*(1.04*LOG(B8/2,2)+1.5+IF(MOD(ROUND(K8,0)-1,3)=0,0,1))</f>
-        <v>414.08000000000004</v>
-      </c>
-      <c r="H8" s="1">
-        <f>(E8-F8)/E8</f>
-        <v>0.10744394618834072</v>
-      </c>
-      <c r="I8" s="1">
-        <f t="shared" si="1"/>
-        <v>7.1569506726457302E-2</v>
+        <v>6.7387387387387296E-2</v>
       </c>
       <c r="J8" s="1">
         <v>16</v>
       </c>
       <c r="K8" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>15.84</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B9" s="1">
         <v>8192</v>
       </c>
       <c r="C9" s="1">
-        <v>510</v>
+        <v>480</v>
       </c>
       <c r="D9" s="1">
-        <v>475</v>
+        <v>446</v>
       </c>
       <c r="E9" s="1">
+        <f t="shared" si="5"/>
+        <v>926</v>
+      </c>
+      <c r="F9" s="2">
+        <f t="shared" si="2"/>
+        <v>862.72</v>
+      </c>
+      <c r="G9" s="2">
+        <f t="shared" si="0"/>
+        <v>958.72</v>
+      </c>
+      <c r="H9" s="1">
+        <f t="shared" si="1"/>
+        <v>6.8336933045356346E-2</v>
+      </c>
+      <c r="I9" s="1">
         <f t="shared" si="3"/>
-        <v>985</v>
-      </c>
-      <c r="F9" s="2">
-        <f t="shared" si="0"/>
-        <v>862.72</v>
-      </c>
-      <c r="G9" s="2">
-        <f>(2*B9/$A$2)*(1.04*LOG(B9/2,2)+1.5+IF(MOD(ROUND(K9,0)-1,3)=0,0,1))</f>
-        <v>958.72</v>
-      </c>
-      <c r="H9" s="1">
-        <f>(E9-F9)/E9</f>
-        <v>0.1241421319796954</v>
-      </c>
-      <c r="I9" s="1">
-        <f t="shared" si="1"/>
-        <v>2.668020304568525E-2</v>
+        <v>-3.533477321814258E-2</v>
       </c>
       <c r="J9" s="1">
         <v>17</v>
       </c>
       <c r="K9" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>17.28</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B10" s="1">
         <f>8192*2</f>
         <v>16384</v>
@@ -1952,264 +1952,271 @@
         <v>974</v>
       </c>
       <c r="E10" s="1">
+        <f t="shared" si="5"/>
+        <v>2014</v>
+      </c>
+      <c r="F10" s="2">
+        <f t="shared" si="2"/>
+        <v>1858.56</v>
+      </c>
+      <c r="G10" s="2">
+        <f t="shared" si="0"/>
+        <v>1922.56</v>
+      </c>
+      <c r="H10" s="1">
+        <f t="shared" si="1"/>
+        <v>7.7179741807348587E-2</v>
+      </c>
+      <c r="I10" s="1">
         <f t="shared" si="3"/>
-        <v>2014</v>
-      </c>
-      <c r="F10" s="2">
-        <f t="shared" si="0"/>
-        <v>1858.56</v>
-      </c>
-      <c r="G10" s="2">
-        <f>(2*B10/$A$2)*(1.04*LOG(B10/2,2)+1.5+IF(MOD(ROUND(K10,0)-1,3)=0,0,1))</f>
-        <v>1922.56</v>
-      </c>
-      <c r="H10" s="1">
-        <f>(E10-F10)/E10</f>
-        <v>7.7179741807348587E-2</v>
-      </c>
-      <c r="I10" s="1">
-        <f t="shared" si="1"/>
         <v>4.5402184707050673E-2</v>
       </c>
       <c r="J10" s="1">
         <v>19</v>
       </c>
       <c r="K10" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>18.72</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B11" s="1">
         <f>2*B10</f>
         <v>32768</v>
       </c>
       <c r="C11" s="1">
-        <v>2285</v>
+        <v>2158</v>
       </c>
       <c r="D11" s="1">
-        <v>2154</v>
+        <v>2028</v>
       </c>
       <c r="E11" s="1">
+        <f t="shared" si="5"/>
+        <v>4186</v>
+      </c>
+      <c r="F11" s="2">
+        <f t="shared" si="2"/>
+        <v>3983.36</v>
+      </c>
+      <c r="G11" s="2">
+        <f t="shared" si="0"/>
+        <v>4367.3600000000006</v>
+      </c>
+      <c r="H11" s="1">
+        <f t="shared" si="1"/>
+        <v>4.840898232202577E-2</v>
+      </c>
+      <c r="I11" s="1">
         <f t="shared" si="3"/>
-        <v>4439</v>
-      </c>
-      <c r="F11" s="2">
-        <f t="shared" si="0"/>
-        <v>3983.36</v>
-      </c>
-      <c r="G11" s="2">
-        <f>(2*B11/$A$2)*(1.04*LOG(B11/2,2)+1.5+IF(MOD(ROUND(K11,0)-1,3)=0,0,1))</f>
-        <v>4367.3600000000006</v>
-      </c>
-      <c r="H11" s="1">
-        <f>(E11-F11)/E11</f>
-        <v>0.10264473980626264</v>
-      </c>
-      <c r="I11" s="1">
-        <f t="shared" si="1"/>
-        <v>1.613876999324159E-2</v>
+        <v>-4.3325370281892157E-2</v>
       </c>
       <c r="J11" s="1">
         <v>20</v>
       </c>
       <c r="K11" s="1">
+        <f t="shared" si="4"/>
+        <v>20.16</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B12" s="1">
+        <f t="shared" ref="B12:B16" si="6">2*B11</f>
+        <v>65536</v>
+      </c>
+      <c r="C12" s="1">
+        <v>4666</v>
+      </c>
+      <c r="D12" s="1">
+        <v>4408</v>
+      </c>
+      <c r="E12" s="1">
+        <f t="shared" si="5"/>
+        <v>9074</v>
+      </c>
+      <c r="F12" s="2">
         <f t="shared" si="2"/>
-        <v>20.16</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B12" s="1">
-        <f t="shared" ref="B12:B16" si="4">2*B11</f>
-        <v>65536</v>
-      </c>
-      <c r="C12" s="1">
-        <v>4668</v>
-      </c>
-      <c r="D12" s="1">
-        <v>4410</v>
-      </c>
-      <c r="E12" s="1">
+        <v>8499.2000000000007</v>
+      </c>
+      <c r="G12" s="2">
+        <f t="shared" si="0"/>
+        <v>8755.2000000000007</v>
+      </c>
+      <c r="H12" s="1">
+        <f t="shared" si="1"/>
+        <v>6.3345823231209977E-2</v>
+      </c>
+      <c r="I12" s="1">
         <f t="shared" si="3"/>
-        <v>9078</v>
-      </c>
-      <c r="F12" s="2">
-        <f t="shared" si="0"/>
-        <v>8499.2000000000007</v>
-      </c>
-      <c r="G12" s="2">
-        <f>(2*B12/$A$2)*(1.04*LOG(B12/2,2)+1.5+IF(MOD(ROUND(K12,0)-1,3)=0,0,1))</f>
-        <v>8755.2000000000007</v>
-      </c>
-      <c r="H12" s="1">
-        <f>(E12-F12)/E12</f>
-        <v>6.3758537122714176E-2</v>
-      </c>
-      <c r="I12" s="1">
-        <f t="shared" si="1"/>
-        <v>3.555849306014533E-2</v>
+        <v>3.5133348027330757E-2</v>
       </c>
       <c r="J12" s="1">
         <v>22</v>
       </c>
       <c r="K12" s="1">
+        <f t="shared" si="4"/>
+        <v>21.599999999999998</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B13" s="1">
+        <f t="shared" si="6"/>
+        <v>131072</v>
+      </c>
+      <c r="C13" s="1">
+        <v>9714</v>
+      </c>
+      <c r="D13" s="1">
+        <v>9200</v>
+      </c>
+      <c r="E13" s="1">
+        <f t="shared" si="5"/>
+        <v>18914</v>
+      </c>
+      <c r="F13" s="2">
         <f t="shared" si="2"/>
-        <v>21.599999999999998</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B13" s="1">
-        <f t="shared" si="4"/>
-        <v>131072</v>
-      </c>
-      <c r="C13" s="1">
-        <v>10222</v>
-      </c>
-      <c r="D13" s="1">
-        <v>9707</v>
-      </c>
-      <c r="E13" s="1">
+        <v>18063.36</v>
+      </c>
+      <c r="G13" s="2">
+        <f t="shared" si="0"/>
+        <v>19599.36</v>
+      </c>
+      <c r="H13" s="1">
+        <f t="shared" si="1"/>
+        <v>4.4974093264248671E-2</v>
+      </c>
+      <c r="I13" s="1">
         <f t="shared" si="3"/>
-        <v>19929</v>
-      </c>
-      <c r="F13" s="2">
-        <f t="shared" si="0"/>
-        <v>18063.36</v>
-      </c>
-      <c r="G13" s="2">
-        <f>(2*B13/$A$2)*(1.04*LOG(B13/2,2)+1.5+IF(MOD(ROUND(K13,0)-1,3)=0,0,1))</f>
-        <v>19599.36</v>
-      </c>
-      <c r="H13" s="1">
-        <f>(E13-F13)/E13</f>
-        <v>9.3614330874604815E-2</v>
-      </c>
-      <c r="I13" s="1">
-        <f t="shared" si="1"/>
-        <v>1.6540719554418156E-2</v>
+        <v>-3.6235592682668953E-2</v>
       </c>
       <c r="J13" s="1">
         <v>23</v>
       </c>
       <c r="K13" s="1">
+        <f t="shared" si="4"/>
+        <v>23.04</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B14" s="1">
+        <f t="shared" si="6"/>
+        <v>262144</v>
+      </c>
+      <c r="C14" s="1">
+        <v>20830</v>
+      </c>
+      <c r="D14" s="1">
+        <v>19804</v>
+      </c>
+      <c r="E14" s="1">
+        <f>SUM(C14:D14)</f>
+        <v>40634</v>
+      </c>
+      <c r="F14" s="2">
         <f t="shared" si="2"/>
-        <v>23.04</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B14" s="1">
-        <f t="shared" si="4"/>
-        <v>262144</v>
-      </c>
-      <c r="C14" s="1">
-        <v>20828</v>
-      </c>
-      <c r="D14" s="1">
-        <v>19802</v>
-      </c>
-      <c r="E14" s="1">
+        <v>38256.639999999999</v>
+      </c>
+      <c r="G14" s="2">
+        <f t="shared" si="0"/>
+        <v>41328.639999999999</v>
+      </c>
+      <c r="H14" s="1">
+        <f t="shared" si="1"/>
+        <v>5.8506669291726154E-2</v>
+      </c>
+      <c r="I14" s="1">
         <f t="shared" si="3"/>
-        <v>40630</v>
-      </c>
-      <c r="F14" s="2">
-        <f t="shared" si="0"/>
-        <v>38256.639999999999</v>
-      </c>
-      <c r="G14" s="2">
-        <f>(2*B14/$A$2)*(1.04*LOG(B14/2,2)+1.5+IF(MOD(ROUND(K14,0)-1,3)=0,0,1))</f>
-        <v>41328.639999999999</v>
-      </c>
-      <c r="H14" s="1">
-        <f>(E14-F14)/E14</f>
-        <v>5.8413979817868583E-2</v>
-      </c>
-      <c r="I14" s="1">
-        <f t="shared" si="1"/>
-        <v>-1.7195175978341113E-2</v>
+        <v>-1.7095043559580633E-2</v>
       </c>
       <c r="J14" s="1">
         <v>25</v>
       </c>
       <c r="K14" s="1">
+        <f t="shared" si="4"/>
+        <v>24.48</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B15" s="1">
+        <f t="shared" si="6"/>
+        <v>524288</v>
+      </c>
+      <c r="C15" s="1">
+        <v>43258</v>
+      </c>
+      <c r="D15" s="1">
+        <v>41208</v>
+      </c>
+      <c r="E15" s="1">
+        <f t="shared" si="5"/>
+        <v>84466</v>
+      </c>
+      <c r="F15" s="2">
         <f t="shared" si="2"/>
-        <v>24.48</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B15" s="1">
-        <f t="shared" si="4"/>
-        <v>524288</v>
-      </c>
-      <c r="C15" s="1">
-        <v>45308</v>
-      </c>
-      <c r="D15" s="1">
-        <v>43257</v>
-      </c>
-      <c r="E15" s="1">
+        <v>80773.119999999995</v>
+      </c>
+      <c r="G15" s="2">
+        <f t="shared" si="0"/>
+        <v>86917.119999999995</v>
+      </c>
+      <c r="H15" s="1">
+        <f t="shared" si="1"/>
+        <v>4.3720313498922699E-2</v>
+      </c>
+      <c r="I15" s="1">
         <f t="shared" si="3"/>
-        <v>88565</v>
-      </c>
-      <c r="F15" s="2">
-        <f t="shared" si="0"/>
-        <v>80773.119999999995</v>
-      </c>
-      <c r="G15" s="2">
-        <f>(2*B15/$A$2)*(1.04*LOG(B15/2,2)+1.5+IF(MOD(ROUND(K15,0)-1,3)=0,0,1))</f>
-        <v>86917.119999999995</v>
-      </c>
-      <c r="H15" s="1">
-        <f>(E15-F15)/E15</f>
-        <v>8.7979224298537856E-2</v>
-      </c>
-      <c r="I15" s="1">
-        <f t="shared" si="1"/>
-        <v>1.8606447242138596E-2</v>
+        <v>-2.901901356758927E-2</v>
       </c>
       <c r="J15" s="1">
         <v>26</v>
       </c>
       <c r="K15" s="1">
+        <f t="shared" si="4"/>
+        <v>25.919999999999998</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B16" s="1">
+        <f t="shared" si="6"/>
+        <v>1048576</v>
+      </c>
+      <c r="C16" s="1">
+        <v>91833</v>
+      </c>
+      <c r="D16" s="1">
+        <v>87785</v>
+      </c>
+      <c r="E16" s="1">
+        <f t="shared" si="5"/>
+        <v>179618</v>
+      </c>
+      <c r="F16" s="2">
         <f t="shared" si="2"/>
-        <v>25.919999999999998</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B16" s="1">
-        <f t="shared" si="4"/>
-        <v>1048576</v>
-      </c>
-      <c r="E16" s="1">
+        <v>170065.92000000001</v>
+      </c>
+      <c r="G16" s="2">
+        <f t="shared" si="0"/>
+        <v>182353.92000000001</v>
+      </c>
+      <c r="H16" s="1">
+        <f t="shared" si="1"/>
+        <v>5.3179970826977181E-2</v>
+      </c>
+      <c r="I16" s="1">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="F16" s="2">
-        <f t="shared" si="0"/>
-        <v>170065.92000000001</v>
-      </c>
-      <c r="G16" s="2">
-        <f>(2*B16/$A$2)*(1.04*LOG(B16/2,2)+1.5+IF(MOD(ROUND(K16,0)-1,3)=0,0,1))</f>
-        <v>182353.92000000001</v>
-      </c>
-      <c r="H16" s="1" t="e">
-        <f>(E16-F16)/E16</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I16" s="1" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
+        <v>-1.5231880991882845E-2</v>
       </c>
       <c r="J16" s="1"/>
       <c r="K16" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>27.36</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
   <ignoredErrors>
     <ignoredError sqref="E2:E9" formulaRange="1"/>
   </ignoredErrors>
-  <drawing r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/Pomiary.xlsx
+++ b/Pomiary.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a3eea4af91086274/Pulpit/SEM5/SBD/P1/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="27" documentId="8_{2FCF4A24-72F7-4805-86B8-F02B7F7B739A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B432F5D7-AA74-47C7-A04E-2FA9670C920D}"/>
+  <xr:revisionPtr revIDLastSave="187" documentId="8_{2FCF4A24-72F7-4805-86B8-F02B7F7B739A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A78E966F-B154-4E5B-ABA8-0823237D6869}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{63E0899F-1F7B-41C1-81BE-D2DEB1B2E785}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{63E0899F-1F7B-41C1-81BE-D2DEB1B2E785}"/>
   </bookViews>
   <sheets>
     <sheet name="Arkusz1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="14">
   <si>
     <t>N</t>
   </si>
@@ -65,18 +65,30 @@
     <t>Błąd</t>
   </si>
   <si>
-    <t>R+W (teor.2)</t>
+    <t>Fazy v2</t>
   </si>
   <si>
-    <t>Błąd 2</t>
+    <t>phi</t>
+  </si>
+  <si>
+    <t>współ.</t>
+  </si>
+  <si>
+    <t>Ilość faz</t>
+  </si>
+  <si>
+    <t>Ilość faz (teor.)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="#,##0.00\ _z_ł"/>
+    <numFmt numFmtId="167" formatCode="#,##0_ ;\-#,##0\ "/>
+    <numFmt numFmtId="168" formatCode="#,##0.00_ ;\-#,##0.00\ "/>
+    <numFmt numFmtId="169" formatCode="#,##0.000_ ;\-#,##0.000\ "/>
   </numFmts>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
@@ -108,12 +120,21 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -149,7 +170,17 @@
   <c:chart>
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
-      <c:layout/>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.11377607853663099"/>
+          <c:y val="2.7261462205700124E-2"/>
+          <c:w val="0.79307327021280805"/>
+          <c:h val="0.82434914966484207"/>
+        </c:manualLayout>
+      </c:layout>
       <c:scatterChart>
         <c:scatterStyle val="lineMarker"/>
         <c:varyColors val="0"/>
@@ -309,7 +340,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>Arkusz1!$F$1</c:f>
+              <c:f>Arkusz1!$K$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -396,54 +427,54 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Arkusz1!$F$2:$F$16</c:f>
+              <c:f>Arkusz1!$K$2:$K$16</c:f>
               <c:numCache>
-                <c:formatCode>#\ ##0.00\ _z_ł</c:formatCode>
+                <c:formatCode>General</c:formatCode>
                 <c:ptCount val="15"/>
                 <c:pt idx="0">
-                  <c:v>3.1</c:v>
+                  <c:v>13.130495168499705</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>7.24</c:v>
+                  <c:v>16.02492235949962</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>16.560000000000002</c:v>
+                  <c:v>17.47213595499958</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>37.28</c:v>
+                  <c:v>40.733126291998985</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>82.88</c:v>
+                  <c:v>87.255106965997811</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>182.4</c:v>
+                  <c:v>197.66563145999496</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>398.08000000000004</c:v>
+                  <c:v>418.48668044798922</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>862.72</c:v>
+                  <c:v>883.28419595197704</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1858.56</c:v>
+                  <c:v>1951.8117321279487</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>3983.36</c:v>
+                  <c:v>4088.8668044798924</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>8499.2000000000007</c:v>
+                  <c:v>8918.7069698557625</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>18063.36</c:v>
+                  <c:v>18578.387300607505</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>38256.639999999999</c:v>
+                  <c:v>40120.66804479892</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>80773.119999999995</c:v>
+                  <c:v>83205.229533181759</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>170065.92000000001</c:v>
+                  <c:v>178266.03284069916</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -488,6 +519,61 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="pl-PL"/>
+                  <a:t>N</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="pl-PL"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
@@ -551,6 +637,66 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="pl-PL"/>
+                  <a:t>Liczba</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="pl-PL" baseline="0"/>
+                  <a:t> operacji dyskowych</a:t>
+                </a:r>
+                <a:endParaRPr lang="pl-PL"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="pl-PL"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
@@ -1272,6 +1418,10 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Motyw pakietu Office">
   <a:themeElements>
@@ -1589,16 +1739,24 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E0FACBD2-E050-4C25-B7F3-B372F54F54CB}">
-  <dimension ref="A1:K16"/>
+  <dimension ref="A1:U34"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="5" width="8.85546875" style="1"/>
     <col min="6" max="6" width="12.85546875" style="2" customWidth="1"/>
     <col min="7" max="7" width="13.42578125" style="2" customWidth="1"/>
     <col min="8" max="8" width="13" style="1" customWidth="1"/>
+    <col min="9" max="9" width="13.140625" customWidth="1"/>
+    <col min="10" max="10" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="16.28515625" customWidth="1"/>
+    <col min="16" max="16" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.7109375" customWidth="1"/>
+    <col min="19" max="19" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="13.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>7</v>
       </c>
@@ -1617,23 +1775,32 @@
       <c r="F1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="H1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>4</v>
-      </c>
       <c r="K1" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+        <v>6</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>256</v>
       </c>
@@ -1654,27 +1821,42 @@
         <f>(2*B2/$A$2)*(1.04*LOG(B2/2,2)+1)</f>
         <v>3.1</v>
       </c>
-      <c r="G2" s="2">
-        <f t="shared" ref="G2:G16" si="0">(2*B2/$A$2)*(1.04*LOG(B2/2,2)+1.5+IF(MOD(ROUND(K2,0)-1,3)=0,0,1))</f>
-        <v>3.35</v>
+      <c r="G2" s="1">
+        <f>(E2-F2)/E2</f>
+        <v>0.83684210526315794</v>
       </c>
       <c r="H2" s="1">
-        <f t="shared" ref="H2:H16" si="1">(E2-F2)/E2</f>
-        <v>0.83684210526315794</v>
+        <v>7</v>
       </c>
       <c r="I2" s="1">
-        <f>(E2-G2)/E2</f>
-        <v>0.8236842105263158</v>
+        <f>LOG(B2/2,$A$5)</f>
+        <v>7.2021004520627816</v>
       </c>
       <c r="J2" s="1">
+        <f>ROUNDUP(I2+LOG(SQRT(5),$A$5),0)-2</f>
         <v>7</v>
       </c>
       <c r="K2" s="1">
-        <f>1.44*LOG(B2/2,2)</f>
-        <v>7.1999999999999993</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+        <f>2*ROUNDUP(B2/$A$2,0)*($A$8*J2+1.5)</f>
+        <v>13.130495168499705</v>
+      </c>
+      <c r="L2" s="1">
+        <f>(E2-K2)/E2</f>
+        <v>0.30892130692106817</v>
+      </c>
+      <c r="P2" s="1">
+        <v>64</v>
+      </c>
+      <c r="Q2" s="1">
+        <v>7</v>
+      </c>
+      <c r="R2" s="1">
+        <f>ROUNDUP(Q2+LOG(SQRT(5),$A$5),0)-2</f>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A3" s="1"/>
       <c r="B3" s="1">
         <v>128</v>
       </c>
@@ -1689,30 +1871,47 @@
         <v>23</v>
       </c>
       <c r="F3" s="2">
-        <f t="shared" ref="F3:F16" si="2">(2*B3/$A$2)*(1.04*LOG(B3/2,2)+1)</f>
+        <f t="shared" ref="F3:F16" si="0">(2*B3/$A$2)*(1.04*LOG(B3/2,2)+1)</f>
         <v>7.24</v>
       </c>
-      <c r="G3" s="2">
-        <f t="shared" si="0"/>
-        <v>8.74</v>
+      <c r="G3" s="1">
+        <f>(E3-F3)/E3</f>
+        <v>0.68521739130434778</v>
       </c>
       <c r="H3" s="1">
-        <f t="shared" si="1"/>
-        <v>0.68521739130434778</v>
+        <v>9</v>
       </c>
       <c r="I3" s="1">
-        <f t="shared" ref="I3:I16" si="3">(E3-G3)/E3</f>
-        <v>0.62</v>
+        <f t="shared" ref="I3:I16" si="1">LOG(B3/2,$A$5)</f>
+        <v>8.6425205424753369</v>
       </c>
       <c r="J3" s="1">
+        <f t="shared" ref="J3:J16" si="2">ROUNDUP(I3+LOG(SQRT(5),$A$5),0)-2</f>
         <v>9</v>
       </c>
       <c r="K3" s="1">
-        <f t="shared" ref="K3:K16" si="4">1.44*LOG(B3/2,2)</f>
-        <v>8.64</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+        <f t="shared" ref="K3:K16" si="3">2*ROUNDUP(B3/$A$2,0)*($A$8*J3+1.5)</f>
+        <v>16.02492235949962</v>
+      </c>
+      <c r="L3" s="1">
+        <f t="shared" ref="L3:L16" si="4">(E3-K3)/E3</f>
+        <v>0.30326424523914697</v>
+      </c>
+      <c r="P3" s="1">
+        <v>128</v>
+      </c>
+      <c r="Q3" s="1">
+        <v>9</v>
+      </c>
+      <c r="R3" s="1">
+        <f t="shared" ref="R3:R16" si="5">ROUNDUP(Q3+LOG(SQRT(5),$A$5),0)-2</f>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>10</v>
+      </c>
       <c r="B4" s="1">
         <v>256</v>
       </c>
@@ -1723,34 +1922,52 @@
         <v>12</v>
       </c>
       <c r="E4" s="1">
-        <f t="shared" ref="E4:E16" si="5">SUM(C4:D4)</f>
+        <f t="shared" ref="E4:E16" si="6">SUM(C4:D4)</f>
         <v>27</v>
       </c>
       <c r="F4" s="2">
+        <f t="shared" si="0"/>
+        <v>16.560000000000002</v>
+      </c>
+      <c r="G4" s="1">
+        <f>(E4-F4)/E4</f>
+        <v>0.3866666666666666</v>
+      </c>
+      <c r="H4" s="1">
+        <v>10</v>
+      </c>
+      <c r="I4" s="1">
+        <f t="shared" si="1"/>
+        <v>10.082940632887894</v>
+      </c>
+      <c r="J4" s="1">
         <f t="shared" si="2"/>
-        <v>16.560000000000002</v>
-      </c>
-      <c r="G4" s="2">
-        <f t="shared" si="0"/>
-        <v>17.560000000000002</v>
-      </c>
-      <c r="H4" s="1">
-        <f t="shared" si="1"/>
-        <v>0.3866666666666666</v>
-      </c>
-      <c r="I4" s="1">
+        <v>10</v>
+      </c>
+      <c r="K4" s="1">
         <f t="shared" si="3"/>
-        <v>0.34962962962962957</v>
-      </c>
-      <c r="J4" s="1">
+        <v>17.47213595499958</v>
+      </c>
+      <c r="L4" s="1">
+        <f t="shared" si="4"/>
+        <v>0.35288385351853407</v>
+      </c>
+      <c r="P4" s="1">
+        <v>256</v>
+      </c>
+      <c r="Q4" s="1">
         <v>10</v>
       </c>
-      <c r="K4" s="1">
-        <f t="shared" si="4"/>
-        <v>10.08</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="R4" s="1">
+        <f t="shared" si="5"/>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
+        <f>(1+SQRT(5))/2</f>
+        <v>1.6180339887498949</v>
+      </c>
       <c r="B5" s="1">
         <v>512</v>
       </c>
@@ -1761,34 +1978,48 @@
         <v>27</v>
       </c>
       <c r="E5" s="1">
+        <f t="shared" si="6"/>
+        <v>58</v>
+      </c>
+      <c r="F5" s="2">
+        <f t="shared" si="0"/>
+        <v>37.28</v>
+      </c>
+      <c r="G5" s="1">
+        <f>(E5-F5)/E5</f>
+        <v>0.35724137931034483</v>
+      </c>
+      <c r="H5" s="1">
+        <v>12</v>
+      </c>
+      <c r="I5" s="1">
+        <f t="shared" si="1"/>
+        <v>11.523360723300451</v>
+      </c>
+      <c r="J5" s="1">
+        <f t="shared" si="2"/>
+        <v>12</v>
+      </c>
+      <c r="K5" s="1">
+        <f t="shared" si="3"/>
+        <v>40.733126291998985</v>
+      </c>
+      <c r="L5" s="1">
+        <f t="shared" si="4"/>
+        <v>0.29770471910346574</v>
+      </c>
+      <c r="P5" s="1">
+        <v>512</v>
+      </c>
+      <c r="Q5" s="1">
+        <v>12</v>
+      </c>
+      <c r="R5" s="1">
         <f t="shared" si="5"/>
-        <v>58</v>
-      </c>
-      <c r="F5" s="2">
-        <f t="shared" si="2"/>
-        <v>37.28</v>
-      </c>
-      <c r="G5" s="2">
-        <f t="shared" si="0"/>
-        <v>43.28</v>
-      </c>
-      <c r="H5" s="1">
-        <f t="shared" si="1"/>
-        <v>0.35724137931034483</v>
-      </c>
-      <c r="I5" s="1">
-        <f t="shared" si="3"/>
-        <v>0.25379310344827583</v>
-      </c>
-      <c r="J5" s="1">
         <v>12</v>
       </c>
-      <c r="K5" s="1">
-        <f t="shared" si="4"/>
-        <v>11.52</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
       <c r="B6" s="1">
         <v>1024</v>
       </c>
@@ -1799,34 +2030,51 @@
         <v>47</v>
       </c>
       <c r="E6" s="1">
+        <f t="shared" si="6"/>
+        <v>100</v>
+      </c>
+      <c r="F6" s="2">
+        <f t="shared" si="0"/>
+        <v>82.88</v>
+      </c>
+      <c r="G6" s="1">
+        <f>(E6-F6)/E6</f>
+        <v>0.17120000000000005</v>
+      </c>
+      <c r="H6" s="1">
+        <v>13</v>
+      </c>
+      <c r="I6" s="1">
+        <f t="shared" si="1"/>
+        <v>12.963780813713008</v>
+      </c>
+      <c r="J6" s="1">
+        <f t="shared" si="2"/>
+        <v>13</v>
+      </c>
+      <c r="K6" s="1">
+        <f t="shared" si="3"/>
+        <v>87.255106965997811</v>
+      </c>
+      <c r="L6" s="1">
+        <f t="shared" si="4"/>
+        <v>0.12744893034002189</v>
+      </c>
+      <c r="P6" s="1">
+        <v>1024</v>
+      </c>
+      <c r="Q6" s="1">
+        <v>13</v>
+      </c>
+      <c r="R6" s="1">
         <f t="shared" si="5"/>
-        <v>100</v>
-      </c>
-      <c r="F6" s="2">
-        <f t="shared" si="2"/>
-        <v>82.88</v>
-      </c>
-      <c r="G6" s="2">
-        <f>(2*B6/$A$2)*(1.04*LOG(B6/2,2)+1.5+IF(MOD(ROUND(K6,0)-1,3)=0,0,1))</f>
-        <v>86.88</v>
-      </c>
-      <c r="H6" s="1">
-        <f t="shared" si="1"/>
-        <v>0.17120000000000005</v>
-      </c>
-      <c r="I6" s="1">
-        <f t="shared" si="3"/>
-        <v>0.13120000000000004</v>
-      </c>
-      <c r="J6" s="1">
         <v>13</v>
       </c>
-      <c r="K6" s="1">
-        <f t="shared" si="4"/>
-        <v>12.959999999999999</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>11</v>
+      </c>
       <c r="B7" s="1">
         <v>2048</v>
       </c>
@@ -1837,34 +2085,52 @@
         <v>102</v>
       </c>
       <c r="E7" s="1">
+        <f t="shared" si="6"/>
+        <v>214</v>
+      </c>
+      <c r="F7" s="2">
+        <f t="shared" si="0"/>
+        <v>182.4</v>
+      </c>
+      <c r="G7" s="1">
+        <f>(E7-F7)/E7</f>
+        <v>0.14766355140186913</v>
+      </c>
+      <c r="H7" s="1">
+        <v>15</v>
+      </c>
+      <c r="I7" s="1">
+        <f t="shared" si="1"/>
+        <v>14.404200904125563</v>
+      </c>
+      <c r="J7" s="1">
+        <f t="shared" si="2"/>
+        <v>15</v>
+      </c>
+      <c r="K7" s="1">
+        <f t="shared" si="3"/>
+        <v>197.66563145999496</v>
+      </c>
+      <c r="L7" s="1">
+        <f t="shared" si="4"/>
+        <v>7.6328824953294599E-2</v>
+      </c>
+      <c r="P7" s="1">
+        <v>2048</v>
+      </c>
+      <c r="Q7" s="1">
+        <v>15</v>
+      </c>
+      <c r="R7" s="1">
         <f t="shared" si="5"/>
-        <v>214</v>
-      </c>
-      <c r="F7" s="2">
-        <f t="shared" si="2"/>
-        <v>182.4</v>
-      </c>
-      <c r="G7" s="2">
-        <f t="shared" si="0"/>
-        <v>206.4</v>
-      </c>
-      <c r="H7" s="1">
-        <f t="shared" si="1"/>
-        <v>0.14766355140186913</v>
-      </c>
-      <c r="I7" s="1">
-        <f t="shared" si="3"/>
-        <v>3.551401869158876E-2</v>
-      </c>
-      <c r="J7" s="1">
         <v>15</v>
       </c>
-      <c r="K7" s="1">
-        <f t="shared" si="4"/>
-        <v>14.399999999999999</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A8" s="1">
+        <f>(1+A5) / (1+A5*A5)</f>
+        <v>0.72360679774997894</v>
+      </c>
       <c r="B8" s="1">
         <v>4096</v>
       </c>
@@ -1875,34 +2141,48 @@
         <v>213</v>
       </c>
       <c r="E8" s="1">
+        <f t="shared" si="6"/>
+        <v>444</v>
+      </c>
+      <c r="F8" s="2">
+        <f t="shared" si="0"/>
+        <v>398.08000000000004</v>
+      </c>
+      <c r="G8" s="1">
+        <f>(E8-F8)/E8</f>
+        <v>0.10342342342342332</v>
+      </c>
+      <c r="H8" s="1">
+        <v>16</v>
+      </c>
+      <c r="I8" s="1">
+        <f t="shared" si="1"/>
+        <v>15.84462099453812</v>
+      </c>
+      <c r="J8" s="1">
+        <f t="shared" si="2"/>
+        <v>16</v>
+      </c>
+      <c r="K8" s="1">
+        <f t="shared" si="3"/>
+        <v>418.48668044798922</v>
+      </c>
+      <c r="L8" s="1">
+        <f t="shared" si="4"/>
+        <v>5.7462431423447716E-2</v>
+      </c>
+      <c r="P8" s="1">
+        <v>4096</v>
+      </c>
+      <c r="Q8" s="1">
+        <v>16</v>
+      </c>
+      <c r="R8" s="1">
         <f t="shared" si="5"/>
-        <v>444</v>
-      </c>
-      <c r="F8" s="2">
-        <f t="shared" si="2"/>
-        <v>398.08000000000004</v>
-      </c>
-      <c r="G8" s="2">
-        <f t="shared" si="0"/>
-        <v>414.08000000000004</v>
-      </c>
-      <c r="H8" s="1">
-        <f t="shared" si="1"/>
-        <v>0.10342342342342332</v>
-      </c>
-      <c r="I8" s="1">
-        <f t="shared" si="3"/>
-        <v>6.7387387387387296E-2</v>
-      </c>
-      <c r="J8" s="1">
         <v>16</v>
       </c>
-      <c r="K8" s="1">
-        <f t="shared" si="4"/>
-        <v>15.84</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
       <c r="B9" s="1">
         <v>8192</v>
       </c>
@@ -1913,34 +2193,48 @@
         <v>446</v>
       </c>
       <c r="E9" s="1">
+        <f t="shared" si="6"/>
+        <v>926</v>
+      </c>
+      <c r="F9" s="2">
+        <f t="shared" si="0"/>
+        <v>862.72</v>
+      </c>
+      <c r="G9" s="1">
+        <f>(E9-F9)/E9</f>
+        <v>6.8336933045356346E-2</v>
+      </c>
+      <c r="H9" s="1">
+        <v>17</v>
+      </c>
+      <c r="I9" s="1">
+        <f t="shared" si="1"/>
+        <v>17.285041084950674</v>
+      </c>
+      <c r="J9" s="1">
+        <f t="shared" si="2"/>
+        <v>17</v>
+      </c>
+      <c r="K9" s="1">
+        <f t="shared" si="3"/>
+        <v>883.28419595197704</v>
+      </c>
+      <c r="L9" s="1">
+        <f t="shared" si="4"/>
+        <v>4.612937802162307E-2</v>
+      </c>
+      <c r="P9" s="1">
+        <v>8192</v>
+      </c>
+      <c r="Q9" s="1">
+        <v>17</v>
+      </c>
+      <c r="R9" s="1">
         <f t="shared" si="5"/>
-        <v>926</v>
-      </c>
-      <c r="F9" s="2">
-        <f t="shared" si="2"/>
-        <v>862.72</v>
-      </c>
-      <c r="G9" s="2">
-        <f t="shared" si="0"/>
-        <v>958.72</v>
-      </c>
-      <c r="H9" s="1">
-        <f t="shared" si="1"/>
-        <v>6.8336933045356346E-2</v>
-      </c>
-      <c r="I9" s="1">
-        <f t="shared" si="3"/>
-        <v>-3.533477321814258E-2</v>
-      </c>
-      <c r="J9" s="1">
         <v>17</v>
       </c>
-      <c r="K9" s="1">
-        <f t="shared" si="4"/>
-        <v>17.28</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
       <c r="B10" s="1">
         <f>8192*2</f>
         <v>16384</v>
@@ -1952,34 +2246,49 @@
         <v>974</v>
       </c>
       <c r="E10" s="1">
+        <f t="shared" si="6"/>
+        <v>2014</v>
+      </c>
+      <c r="F10" s="2">
+        <f t="shared" si="0"/>
+        <v>1858.56</v>
+      </c>
+      <c r="G10" s="1">
+        <f>(E10-F10)/E10</f>
+        <v>7.7179741807348587E-2</v>
+      </c>
+      <c r="H10" s="1">
+        <v>19</v>
+      </c>
+      <c r="I10" s="1">
+        <f t="shared" si="1"/>
+        <v>18.725461175363233</v>
+      </c>
+      <c r="J10" s="1">
+        <f t="shared" si="2"/>
+        <v>19</v>
+      </c>
+      <c r="K10" s="1">
+        <f t="shared" si="3"/>
+        <v>1951.8117321279487</v>
+      </c>
+      <c r="L10" s="1">
+        <f t="shared" si="4"/>
+        <v>3.0877988019886424E-2</v>
+      </c>
+      <c r="P10" s="1">
+        <f>8192*2</f>
+        <v>16384</v>
+      </c>
+      <c r="Q10" s="1">
+        <v>19</v>
+      </c>
+      <c r="R10" s="1">
         <f t="shared" si="5"/>
-        <v>2014</v>
-      </c>
-      <c r="F10" s="2">
-        <f t="shared" si="2"/>
-        <v>1858.56</v>
-      </c>
-      <c r="G10" s="2">
-        <f t="shared" si="0"/>
-        <v>1922.56</v>
-      </c>
-      <c r="H10" s="1">
-        <f t="shared" si="1"/>
-        <v>7.7179741807348587E-2</v>
-      </c>
-      <c r="I10" s="1">
-        <f t="shared" si="3"/>
-        <v>4.5402184707050673E-2</v>
-      </c>
-      <c r="J10" s="1">
         <v>19</v>
       </c>
-      <c r="K10" s="1">
-        <f t="shared" si="4"/>
-        <v>18.72</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
       <c r="B11" s="1">
         <f>2*B10</f>
         <v>32768</v>
@@ -1991,36 +2300,51 @@
         <v>2028</v>
       </c>
       <c r="E11" s="1">
+        <f t="shared" si="6"/>
+        <v>4186</v>
+      </c>
+      <c r="F11" s="2">
+        <f t="shared" si="0"/>
+        <v>3983.36</v>
+      </c>
+      <c r="G11" s="1">
+        <f>(E11-F11)/E11</f>
+        <v>4.840898232202577E-2</v>
+      </c>
+      <c r="H11" s="1">
+        <v>20</v>
+      </c>
+      <c r="I11" s="1">
+        <f t="shared" si="1"/>
+        <v>20.165881265775788</v>
+      </c>
+      <c r="J11" s="1">
+        <f t="shared" si="2"/>
+        <v>20</v>
+      </c>
+      <c r="K11" s="1">
+        <f t="shared" si="3"/>
+        <v>4088.8668044798924</v>
+      </c>
+      <c r="L11" s="1">
+        <f t="shared" si="4"/>
+        <v>2.3204298977569905E-2</v>
+      </c>
+      <c r="P11" s="1">
+        <f>2*P10</f>
+        <v>32768</v>
+      </c>
+      <c r="Q11" s="1">
+        <v>20</v>
+      </c>
+      <c r="R11" s="1">
         <f t="shared" si="5"/>
-        <v>4186</v>
-      </c>
-      <c r="F11" s="2">
-        <f t="shared" si="2"/>
-        <v>3983.36</v>
-      </c>
-      <c r="G11" s="2">
-        <f t="shared" si="0"/>
-        <v>4367.3600000000006</v>
-      </c>
-      <c r="H11" s="1">
-        <f t="shared" si="1"/>
-        <v>4.840898232202577E-2</v>
-      </c>
-      <c r="I11" s="1">
-        <f t="shared" si="3"/>
-        <v>-4.3325370281892157E-2</v>
-      </c>
-      <c r="J11" s="1">
         <v>20</v>
       </c>
-      <c r="K11" s="1">
-        <f t="shared" si="4"/>
-        <v>20.16</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
       <c r="B12" s="1">
-        <f t="shared" ref="B12:B16" si="6">2*B11</f>
+        <f t="shared" ref="B12:B16" si="7">2*B11</f>
         <v>65536</v>
       </c>
       <c r="C12" s="1">
@@ -2030,36 +2354,51 @@
         <v>4408</v>
       </c>
       <c r="E12" s="1">
+        <f t="shared" si="6"/>
+        <v>9074</v>
+      </c>
+      <c r="F12" s="2">
+        <f t="shared" si="0"/>
+        <v>8499.2000000000007</v>
+      </c>
+      <c r="G12" s="1">
+        <f>(E12-F12)/E12</f>
+        <v>6.3345823231209977E-2</v>
+      </c>
+      <c r="H12" s="1">
+        <v>22</v>
+      </c>
+      <c r="I12" s="1">
+        <f t="shared" si="1"/>
+        <v>21.606301356188347</v>
+      </c>
+      <c r="J12" s="1">
+        <f t="shared" si="2"/>
+        <v>22</v>
+      </c>
+      <c r="K12" s="1">
+        <f t="shared" si="3"/>
+        <v>8918.7069698557625</v>
+      </c>
+      <c r="L12" s="1">
+        <f t="shared" si="4"/>
+        <v>1.7114065477654563E-2</v>
+      </c>
+      <c r="P12" s="1">
+        <f t="shared" ref="P12:P15" si="8">2*P11</f>
+        <v>65536</v>
+      </c>
+      <c r="Q12" s="1">
+        <v>22</v>
+      </c>
+      <c r="R12" s="1">
         <f t="shared" si="5"/>
-        <v>9074</v>
-      </c>
-      <c r="F12" s="2">
-        <f t="shared" si="2"/>
-        <v>8499.2000000000007</v>
-      </c>
-      <c r="G12" s="2">
-        <f t="shared" si="0"/>
-        <v>8755.2000000000007</v>
-      </c>
-      <c r="H12" s="1">
-        <f t="shared" si="1"/>
-        <v>6.3345823231209977E-2</v>
-      </c>
-      <c r="I12" s="1">
-        <f t="shared" si="3"/>
-        <v>3.5133348027330757E-2</v>
-      </c>
-      <c r="J12" s="1">
         <v>22</v>
       </c>
-      <c r="K12" s="1">
-        <f t="shared" si="4"/>
-        <v>21.599999999999998</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
       <c r="B13" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>131072</v>
       </c>
       <c r="C13" s="1">
@@ -2069,36 +2408,51 @@
         <v>9200</v>
       </c>
       <c r="E13" s="1">
+        <f t="shared" si="6"/>
+        <v>18914</v>
+      </c>
+      <c r="F13" s="2">
+        <f t="shared" si="0"/>
+        <v>18063.36</v>
+      </c>
+      <c r="G13" s="1">
+        <f>(E13-F13)/E13</f>
+        <v>4.4974093264248671E-2</v>
+      </c>
+      <c r="H13" s="1">
+        <v>23</v>
+      </c>
+      <c r="I13" s="1">
+        <f t="shared" si="1"/>
+        <v>23.046721446600902</v>
+      </c>
+      <c r="J13" s="1">
+        <f t="shared" si="2"/>
+        <v>23</v>
+      </c>
+      <c r="K13" s="1">
+        <f t="shared" si="3"/>
+        <v>18578.387300607505</v>
+      </c>
+      <c r="L13" s="1">
+        <f t="shared" si="4"/>
+        <v>1.7744141873347542E-2</v>
+      </c>
+      <c r="P13" s="1">
+        <f t="shared" si="8"/>
+        <v>131072</v>
+      </c>
+      <c r="Q13" s="1">
+        <v>23</v>
+      </c>
+      <c r="R13" s="1">
         <f t="shared" si="5"/>
-        <v>18914</v>
-      </c>
-      <c r="F13" s="2">
-        <f t="shared" si="2"/>
-        <v>18063.36</v>
-      </c>
-      <c r="G13" s="2">
-        <f t="shared" si="0"/>
-        <v>19599.36</v>
-      </c>
-      <c r="H13" s="1">
-        <f t="shared" si="1"/>
-        <v>4.4974093264248671E-2</v>
-      </c>
-      <c r="I13" s="1">
-        <f t="shared" si="3"/>
-        <v>-3.6235592682668953E-2</v>
-      </c>
-      <c r="J13" s="1">
         <v>23</v>
       </c>
-      <c r="K13" s="1">
-        <f t="shared" si="4"/>
-        <v>23.04</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
       <c r="B14" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>262144</v>
       </c>
       <c r="C14" s="1">
@@ -2112,32 +2466,47 @@
         <v>40634</v>
       </c>
       <c r="F14" s="2">
+        <f t="shared" si="0"/>
+        <v>38256.639999999999</v>
+      </c>
+      <c r="G14" s="1">
+        <f>(E14-F14)/E14</f>
+        <v>5.8506669291726154E-2</v>
+      </c>
+      <c r="H14" s="1">
+        <v>25</v>
+      </c>
+      <c r="I14" s="1">
+        <f t="shared" si="1"/>
+        <v>24.487141537013457</v>
+      </c>
+      <c r="J14" s="1">
         <f t="shared" si="2"/>
-        <v>38256.639999999999</v>
-      </c>
-      <c r="G14" s="2">
-        <f t="shared" si="0"/>
-        <v>41328.639999999999</v>
-      </c>
-      <c r="H14" s="1">
-        <f t="shared" si="1"/>
-        <v>5.8506669291726154E-2</v>
-      </c>
-      <c r="I14" s="1">
+        <v>25</v>
+      </c>
+      <c r="K14" s="1">
         <f t="shared" si="3"/>
-        <v>-1.7095043559580633E-2</v>
-      </c>
-      <c r="J14" s="1">
+        <v>40120.66804479892</v>
+      </c>
+      <c r="L14" s="1">
+        <f t="shared" si="4"/>
+        <v>1.2633064802901014E-2</v>
+      </c>
+      <c r="P14" s="1">
+        <f t="shared" si="8"/>
+        <v>262144</v>
+      </c>
+      <c r="Q14" s="1">
         <v>25</v>
       </c>
-      <c r="K14" s="1">
-        <f t="shared" si="4"/>
-        <v>24.48</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="R14" s="1">
+        <f t="shared" si="5"/>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
       <c r="B15" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>524288</v>
       </c>
       <c r="C15" s="1">
@@ -2147,36 +2516,51 @@
         <v>41208</v>
       </c>
       <c r="E15" s="1">
+        <f t="shared" si="6"/>
+        <v>84466</v>
+      </c>
+      <c r="F15" s="2">
+        <f t="shared" si="0"/>
+        <v>80773.119999999995</v>
+      </c>
+      <c r="G15" s="1">
+        <f>(E15-F15)/E15</f>
+        <v>4.3720313498922699E-2</v>
+      </c>
+      <c r="H15" s="1">
+        <v>26</v>
+      </c>
+      <c r="I15" s="1">
+        <f t="shared" si="1"/>
+        <v>25.927561627426016</v>
+      </c>
+      <c r="J15" s="1">
+        <f t="shared" si="2"/>
+        <v>26</v>
+      </c>
+      <c r="K15" s="1">
+        <f t="shared" si="3"/>
+        <v>83205.229533181759</v>
+      </c>
+      <c r="L15" s="1">
+        <f t="shared" si="4"/>
+        <v>1.4926366429311692E-2</v>
+      </c>
+      <c r="P15" s="1">
+        <f t="shared" si="8"/>
+        <v>524288</v>
+      </c>
+      <c r="Q15" s="1">
+        <v>26</v>
+      </c>
+      <c r="R15" s="1">
         <f t="shared" si="5"/>
-        <v>84466</v>
-      </c>
-      <c r="F15" s="2">
-        <f t="shared" si="2"/>
-        <v>80773.119999999995</v>
-      </c>
-      <c r="G15" s="2">
-        <f t="shared" si="0"/>
-        <v>86917.119999999995</v>
-      </c>
-      <c r="H15" s="1">
-        <f t="shared" si="1"/>
-        <v>4.3720313498922699E-2</v>
-      </c>
-      <c r="I15" s="1">
-        <f t="shared" si="3"/>
-        <v>-2.901901356758927E-2</v>
-      </c>
-      <c r="J15" s="1">
         <v>26</v>
       </c>
-      <c r="K15" s="1">
-        <f t="shared" si="4"/>
-        <v>25.919999999999998</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
       <c r="B16" s="1">
-        <f t="shared" si="6"/>
+        <f>2*B15</f>
         <v>1048576</v>
       </c>
       <c r="C16" s="1">
@@ -2186,36 +2570,425 @@
         <v>87785</v>
       </c>
       <c r="E16" s="1">
+        <f t="shared" si="6"/>
+        <v>179618</v>
+      </c>
+      <c r="F16" s="2">
+        <f t="shared" si="0"/>
+        <v>170065.92000000001</v>
+      </c>
+      <c r="G16" s="1">
+        <f>(E16-F16)/E16</f>
+        <v>5.3179970826977181E-2</v>
+      </c>
+      <c r="H16" s="1">
+        <v>28</v>
+      </c>
+      <c r="I16" s="1">
+        <f t="shared" si="1"/>
+        <v>27.367981717838571</v>
+      </c>
+      <c r="J16" s="1">
+        <f t="shared" si="2"/>
+        <v>28</v>
+      </c>
+      <c r="K16" s="1">
+        <f t="shared" si="3"/>
+        <v>178266.03284069916</v>
+      </c>
+      <c r="L16" s="1">
+        <f t="shared" si="4"/>
+        <v>7.5269024223676853E-3</v>
+      </c>
+      <c r="P16" s="1">
+        <f>2*P15</f>
+        <v>1048576</v>
+      </c>
+      <c r="Q16" s="1">
+        <v>28</v>
+      </c>
+      <c r="R16" s="1">
         <f t="shared" si="5"/>
+        <v>28</v>
+      </c>
+    </row>
+    <row r="19" spans="16:21" x14ac:dyDescent="0.25">
+      <c r="P19" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q19" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="R19" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="S19" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="T19" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="U19" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="20" spans="16:21" x14ac:dyDescent="0.25">
+      <c r="P20" s="3">
+        <v>64</v>
+      </c>
+      <c r="Q20" s="3">
+        <v>10</v>
+      </c>
+      <c r="R20" s="3">
+        <v>9</v>
+      </c>
+      <c r="S20" s="3">
+        <f>SUM(Q20:R20)</f>
+        <v>19</v>
+      </c>
+      <c r="T20" s="4">
+        <f>K2</f>
+        <v>13.130495168499705</v>
+      </c>
+      <c r="U20" s="5">
+        <f>(MAX(S20:T20)-MIN(S20:T20))/T20</f>
+        <v>0.44701321284374285</v>
+      </c>
+    </row>
+    <row r="21" spans="16:21" x14ac:dyDescent="0.25">
+      <c r="P21" s="3">
+        <v>128</v>
+      </c>
+      <c r="Q21" s="3">
+        <v>12</v>
+      </c>
+      <c r="R21" s="3">
+        <v>11</v>
+      </c>
+      <c r="S21" s="3">
+        <f>SUM(Q21:R21)</f>
+        <v>23</v>
+      </c>
+      <c r="T21" s="4">
+        <f t="shared" ref="T21:T34" si="9">K3</f>
+        <v>16.02492235949962</v>
+      </c>
+      <c r="U21" s="5">
+        <f t="shared" ref="U21:U34" si="10">(MAX(S21:T21)-MIN(S21:T21))/T21</f>
+        <v>0.43526436409631242</v>
+      </c>
+    </row>
+    <row r="22" spans="16:21" x14ac:dyDescent="0.25">
+      <c r="P22" s="3">
+        <v>256</v>
+      </c>
+      <c r="Q22" s="3">
+        <v>15</v>
+      </c>
+      <c r="R22" s="3">
+        <v>12</v>
+      </c>
+      <c r="S22" s="3">
+        <f t="shared" ref="S22:S34" si="11">SUM(Q22:R22)</f>
+        <v>27</v>
+      </c>
+      <c r="T22" s="4">
+        <f t="shared" si="9"/>
+        <v>17.47213595499958</v>
+      </c>
+      <c r="U22" s="5">
+        <f t="shared" si="10"/>
+        <v>0.54531764573833119</v>
+      </c>
+    </row>
+    <row r="23" spans="16:21" x14ac:dyDescent="0.25">
+      <c r="P23" s="3">
+        <v>512</v>
+      </c>
+      <c r="Q23" s="3">
+        <v>31</v>
+      </c>
+      <c r="R23" s="3">
+        <v>27</v>
+      </c>
+      <c r="S23" s="3">
+        <f t="shared" si="11"/>
+        <v>58</v>
+      </c>
+      <c r="T23" s="4">
+        <f t="shared" si="9"/>
+        <v>40.733126291998985</v>
+      </c>
+      <c r="U23" s="5">
+        <f t="shared" si="10"/>
+        <v>0.42390249116215428</v>
+      </c>
+    </row>
+    <row r="24" spans="16:21" x14ac:dyDescent="0.25">
+      <c r="P24" s="3">
+        <v>1024</v>
+      </c>
+      <c r="Q24" s="3">
+        <v>53</v>
+      </c>
+      <c r="R24" s="3">
+        <v>47</v>
+      </c>
+      <c r="S24" s="3">
+        <f t="shared" si="11"/>
+        <v>100</v>
+      </c>
+      <c r="T24" s="4">
+        <f t="shared" si="9"/>
+        <v>87.255106965997811</v>
+      </c>
+      <c r="U24" s="5">
+        <f t="shared" si="10"/>
+        <v>0.1460647230536169</v>
+      </c>
+    </row>
+    <row r="25" spans="16:21" x14ac:dyDescent="0.25">
+      <c r="P25" s="3">
+        <v>2048</v>
+      </c>
+      <c r="Q25" s="3">
+        <v>112</v>
+      </c>
+      <c r="R25" s="3">
+        <v>102</v>
+      </c>
+      <c r="S25" s="3">
+        <f t="shared" si="11"/>
+        <v>214</v>
+      </c>
+      <c r="T25" s="4">
+        <f t="shared" si="9"/>
+        <v>197.66563145999496</v>
+      </c>
+      <c r="U25" s="5">
+        <f t="shared" si="10"/>
+        <v>8.2636361310544346E-2</v>
+      </c>
+    </row>
+    <row r="26" spans="16:21" x14ac:dyDescent="0.25">
+      <c r="P26" s="3">
+        <v>4096</v>
+      </c>
+      <c r="Q26" s="3">
+        <v>231</v>
+      </c>
+      <c r="R26" s="3">
+        <v>213</v>
+      </c>
+      <c r="S26" s="3">
+        <f t="shared" si="11"/>
+        <v>444</v>
+      </c>
+      <c r="T26" s="4">
+        <f t="shared" si="9"/>
+        <v>418.48668044798922</v>
+      </c>
+      <c r="U26" s="5">
+        <f t="shared" si="10"/>
+        <v>6.0965666875463807E-2</v>
+      </c>
+    </row>
+    <row r="27" spans="16:21" x14ac:dyDescent="0.25">
+      <c r="P27" s="3">
+        <v>8192</v>
+      </c>
+      <c r="Q27" s="3">
+        <v>480</v>
+      </c>
+      <c r="R27" s="3">
+        <v>446</v>
+      </c>
+      <c r="S27" s="3">
+        <f t="shared" si="11"/>
+        <v>926</v>
+      </c>
+      <c r="T27" s="4">
+        <f t="shared" si="9"/>
+        <v>883.28419595197704</v>
+      </c>
+      <c r="U27" s="5">
+        <f t="shared" si="10"/>
+        <v>4.836020416054785E-2</v>
+      </c>
+    </row>
+    <row r="28" spans="16:21" x14ac:dyDescent="0.25">
+      <c r="P28" s="3">
+        <f>8192*2</f>
+        <v>16384</v>
+      </c>
+      <c r="Q28" s="3">
+        <v>1040</v>
+      </c>
+      <c r="R28" s="3">
+        <v>974</v>
+      </c>
+      <c r="S28" s="3">
+        <f t="shared" si="11"/>
+        <v>2014</v>
+      </c>
+      <c r="T28" s="4">
+        <f t="shared" si="9"/>
+        <v>1951.8117321279487</v>
+      </c>
+      <c r="U28" s="5">
+        <f t="shared" si="10"/>
+        <v>3.1861816817880764E-2</v>
+      </c>
+    </row>
+    <row r="29" spans="16:21" x14ac:dyDescent="0.25">
+      <c r="P29" s="3">
+        <f>2*P28</f>
+        <v>32768</v>
+      </c>
+      <c r="Q29" s="3">
+        <v>2158</v>
+      </c>
+      <c r="R29" s="3">
+        <v>2028</v>
+      </c>
+      <c r="S29" s="3">
+        <f t="shared" si="11"/>
+        <v>4186</v>
+      </c>
+      <c r="T29" s="4">
+        <f t="shared" si="9"/>
+        <v>4088.8668044798924</v>
+      </c>
+      <c r="U29" s="5">
+        <f t="shared" si="10"/>
+        <v>2.3755529383761145E-2</v>
+      </c>
+    </row>
+    <row r="30" spans="16:21" x14ac:dyDescent="0.25">
+      <c r="P30" s="3">
+        <f t="shared" ref="P30:P33" si="12">2*P29</f>
+        <v>65536</v>
+      </c>
+      <c r="Q30" s="3">
+        <v>4666</v>
+      </c>
+      <c r="R30" s="3">
+        <v>4408</v>
+      </c>
+      <c r="S30" s="3">
+        <f t="shared" si="11"/>
+        <v>9074</v>
+      </c>
+      <c r="T30" s="4">
+        <f t="shared" si="9"/>
+        <v>8918.7069698557625</v>
+      </c>
+      <c r="U30" s="5">
+        <f t="shared" si="10"/>
+        <v>1.741205655361373E-2</v>
+      </c>
+    </row>
+    <row r="31" spans="16:21" x14ac:dyDescent="0.25">
+      <c r="P31" s="3">
+        <f t="shared" si="12"/>
+        <v>131072</v>
+      </c>
+      <c r="Q31" s="3">
+        <v>9714</v>
+      </c>
+      <c r="R31" s="3">
+        <v>9200</v>
+      </c>
+      <c r="S31" s="3">
+        <f t="shared" si="11"/>
+        <v>18914</v>
+      </c>
+      <c r="T31" s="4">
+        <f t="shared" si="9"/>
+        <v>18578.387300607505</v>
+      </c>
+      <c r="U31" s="5">
+        <f t="shared" si="10"/>
+        <v>1.8064684192557502E-2</v>
+      </c>
+    </row>
+    <row r="32" spans="16:21" x14ac:dyDescent="0.25">
+      <c r="P32" s="3">
+        <f t="shared" si="12"/>
+        <v>262144</v>
+      </c>
+      <c r="Q32" s="3">
+        <v>20830</v>
+      </c>
+      <c r="R32" s="3">
+        <v>19804</v>
+      </c>
+      <c r="S32" s="3">
+        <f>SUM(Q32:R32)</f>
+        <v>40634</v>
+      </c>
+      <c r="T32" s="4">
+        <f t="shared" si="9"/>
+        <v>40120.66804479892</v>
+      </c>
+      <c r="U32" s="5">
+        <f t="shared" si="10"/>
+        <v>1.279470109091631E-2</v>
+      </c>
+    </row>
+    <row r="33" spans="16:21" x14ac:dyDescent="0.25">
+      <c r="P33" s="3">
+        <f t="shared" si="12"/>
+        <v>524288</v>
+      </c>
+      <c r="Q33" s="3">
+        <v>43258</v>
+      </c>
+      <c r="R33" s="3">
+        <v>41208</v>
+      </c>
+      <c r="S33" s="3">
+        <f t="shared" si="11"/>
+        <v>84466</v>
+      </c>
+      <c r="T33" s="4">
+        <f t="shared" si="9"/>
+        <v>83205.229533181759</v>
+      </c>
+      <c r="U33" s="5">
+        <f t="shared" si="10"/>
+        <v>1.5152538775407783E-2</v>
+      </c>
+    </row>
+    <row r="34" spans="16:21" x14ac:dyDescent="0.25">
+      <c r="P34" s="3">
+        <f>2*P33</f>
+        <v>1048576</v>
+      </c>
+      <c r="Q34" s="3">
+        <v>91833</v>
+      </c>
+      <c r="R34" s="3">
+        <v>87785</v>
+      </c>
+      <c r="S34" s="3">
+        <f t="shared" si="11"/>
         <v>179618</v>
       </c>
-      <c r="F16" s="2">
-        <f t="shared" si="2"/>
-        <v>170065.92000000001</v>
-      </c>
-      <c r="G16" s="2">
-        <f t="shared" si="0"/>
-        <v>182353.92000000001</v>
-      </c>
-      <c r="H16" s="1">
-        <f t="shared" si="1"/>
-        <v>5.3179970826977181E-2</v>
-      </c>
-      <c r="I16" s="1">
-        <f t="shared" si="3"/>
-        <v>-1.5231880991882845E-2</v>
-      </c>
-      <c r="J16" s="1"/>
-      <c r="K16" s="1">
-        <f t="shared" si="4"/>
-        <v>27.36</v>
+      <c r="T34" s="4">
+        <f t="shared" si="9"/>
+        <v>178266.03284069916</v>
+      </c>
+      <c r="U34" s="5">
+        <f t="shared" si="10"/>
+        <v>7.5839863475784764E-3</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <ignoredErrors>
-    <ignoredError sqref="E2:E9" formulaRange="1"/>
+    <ignoredError sqref="E2:E9 S20:S27" formulaRange="1"/>
   </ignoredErrors>
   <drawing r:id="rId2"/>
 </worksheet>
